--- a/dataset/01.w_Defects/memory_allocation_failure.xlsx
+++ b/dataset/01.w_Defects/memory_allocation_failure.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define ERROR 0x1 #define MAX_V 4294967295UL typedef struct { int *a; int b; } memory_allocation_failure_011_s_001; typedef union { memory_allocation_failure_011_s_001 *s1; memory_allocation_failure_011_s_002 *s2; memory_allocation_failure_011_s_003 *s3; } memory_allocation_failure_011_uni_001; unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_011 () { memory_allocation_failure_011_uni_001 *p =NULL; memory_allocation_failure_011_func_002(); if( memory_allocation_failure_011_gbl_u1 != NULL) { p = memory_allocation_failure_011_gbl_u1; p-&gt;s1-&gt;a[1] = 10; free(memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a); free(memory_allocation_failure_011_gbl_u1-&gt;s1); free(memory_allocation_failure_011_gbl_u1); } } void memory_allocation_failure_011_func_002(void) { memory_allocation_failure_011_gbl_u1 = (memory_allocation_failure_011_uni_001 * )malloc(memory_allocation_failure_011_func_001(0)*sizeof( memory_allocation_failure_011_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_011_gbl_u1-&gt;s1 = (memory_allocation_failure_011_s_001 *) malloc(sizeof(memory_allocation_failure_011_s_001)); memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a = (int *) calloc ( 5,sizeof(int)); } int memory_allocation_failure_011_func_001(int flag) { int ret =0; if (flag ==0) ret = MAX_VAL; else ret=5; return ret; }</t>
+          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define ERROR 0x1 #define MAX_V 4294967295UL typedef union { memory_allocation_failure_011_s_001 *s1; memory_allocation_failure_011_s_002 *s2; memory_allocation_failure_011_s_003 *s3; } memory_allocation_failure_011_uni_001; typedef struct { int *a; int b; } memory_allocation_failure_011_s_001; unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_011 () { memory_allocation_failure_011_uni_001 *p =NULL; memory_allocation_failure_011_func_002(); if( memory_allocation_failure_011_gbl_u1 != NULL) { p = memory_allocation_failure_011_gbl_u1; p-&gt;s1-&gt;a[1] = 10; free(memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a); free(memory_allocation_failure_011_gbl_u1-&gt;s1); free(memory_allocation_failure_011_gbl_u1); } } void memory_allocation_failure_011_func_002(void) { memory_allocation_failure_011_gbl_u1 = (memory_allocation_failure_011_uni_001 * )malloc(memory_allocation_failure_011_func_001(0)*sizeof( memory_allocation_failure_011_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_011_gbl_u1-&gt;s1 = (memory_allocation_failure_011_s_001 *) malloc(sizeof(memory_allocation_failure_011_s_001)); memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a = (int *) calloc ( 5,sizeof(int)); } int memory_allocation_failure_011_func_001(int flag) { int ret =0; if (flag ==0) ret = MAX_VAL; else ret=5; return ret; }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
